--- a/Hoàng/2025/T5/CHI NHÁNH CÔNG TY TNHH AUTOGRILL VFS F&B TẠI ĐÀ NẴNG (78-2025) (TB74-2025)/DS, DM CHI NHÁNH CÔNG TY TNHH AUTOGRILL VFS F&B TẠI ĐÀ NẴNG.xlsx
+++ b/Hoàng/2025/T5/CHI NHÁNH CÔNG TY TNHH AUTOGRILL VFS F&B TẠI ĐÀ NẴNG (78-2025) (TB74-2025)/DS, DM CHI NHÁNH CÔNG TY TNHH AUTOGRILL VFS F&B TẠI ĐÀ NẴNG.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\DATA-TN\Hoàng\2025\T5\CHI NHÁNH CÔNG TY TNHH AUTOGRILL VFS F&amp;B TẠI ĐÀ NẴNG (78-2025)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\DATA-TN\Hoàng\2025\T5\CHI NHÁNH CÔNG TY TNHH AUTOGRILL VFS F&amp;B TẠI ĐÀ NẴNG (78-2025) (TB74-2025)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9EA52CA-149C-4BAB-85E7-691D1B488561}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E73A4FE-9F37-4C0D-8F7D-ABF2D2331095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
